--- a/data/processed/fda_cv_forecasts.xlsx
+++ b/data/processed/fda_cv_forecasts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,19 +486,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.035079</v>
+        <v>0.036596</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001922</v>
+        <v>0.001983</v>
       </c>
       <c r="F2" t="n">
-        <v>15377.479119</v>
+        <v>15524.307918</v>
       </c>
       <c r="G2" t="n">
-        <v>881.765832</v>
+        <v>908.090042</v>
       </c>
       <c r="H2" t="n">
-        <v>103.447286</v>
+        <v>108.045379</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -520,11 +520,11 @@
       <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-07-10
-0       0.000007
-1       0.000007
-2       0.000007
-3       0.000007
-4       0.000007
+0       0.000006
+1       0.000006
+2       0.000006
+3       0.000006
+4       0.000006
 ...          ...
 4996    0.000005
 4997    0.000005
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.053942</v>
+        <v>0.06292200000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003599</v>
+        <v>0.004155</v>
       </c>
       <c r="F3" t="n">
-        <v>21529.650053</v>
+        <v>23381.097177</v>
       </c>
       <c r="G3" t="n">
-        <v>1348.581484</v>
+        <v>1485.478467</v>
       </c>
       <c r="H3" t="n">
-        <v>168.952728</v>
+        <v>189.400448</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -599,11 +599,11 @@
       <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-07-11
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
 ...          ...
 4996    0.000001
 4997    0.000001
@@ -644,19 +644,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.024003</v>
+        <v>0.022197</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001663</v>
+        <v>0.001456</v>
       </c>
       <c r="F4" t="n">
-        <v>14929.945634</v>
+        <v>14052.543638</v>
       </c>
       <c r="G4" t="n">
-        <v>885.727367</v>
+        <v>863.3757000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>90.970051</v>
+        <v>90.98346600000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01126</v>
+        <v>0.012043</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0006089999999999999</v>
+        <v>0.000584</v>
       </c>
       <c r="F5" t="n">
-        <v>6863.807063</v>
+        <v>7163.610678</v>
       </c>
       <c r="G5" t="n">
-        <v>451.060556</v>
+        <v>479.30712</v>
       </c>
       <c r="H5" t="n">
-        <v>58.704058</v>
+        <v>65.168019</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -757,11 +757,11 @@
       <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-07-15
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
 ...          ...
 4996    0.000002
 4997    0.000002
@@ -802,19 +802,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.006939</v>
+        <v>0.007488</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000209</v>
+        <v>0.000157</v>
       </c>
       <c r="F6" t="n">
-        <v>4777.81305</v>
+        <v>4159.005799</v>
       </c>
       <c r="G6" t="n">
-        <v>267.433596</v>
+        <v>237.634545</v>
       </c>
       <c r="H6" t="n">
-        <v>32.73893</v>
+        <v>30.801164</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.004049</v>
+        <v>0.005362</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000105</v>
+        <v>0.000174</v>
       </c>
       <c r="F7" t="n">
-        <v>3918.242772</v>
+        <v>5110.201245</v>
       </c>
       <c r="G7" t="n">
-        <v>235.162603</v>
+        <v>322.275067</v>
       </c>
       <c r="H7" t="n">
-        <v>27.380006</v>
+        <v>40.676302</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -915,11 +915,11 @@
       <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-07-17
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
 ...          ...
 4996    0.000002
 4997    0.000002
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.011753</v>
+        <v>0.014646</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000477</v>
+        <v>0.000768</v>
       </c>
       <c r="F8" t="n">
-        <v>7693.295557</v>
+        <v>9258.372991</v>
       </c>
       <c r="G8" t="n">
-        <v>386.137233</v>
+        <v>523.280126</v>
       </c>
       <c r="H8" t="n">
-        <v>31.444217</v>
+        <v>47.483745</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -994,90 +994,11 @@
       <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-07-18
-0       0.000004
-1       0.000004
-2       0.000004
-3       0.000004
-4       0.000004
-...          ...
-4996    0.000003
-4997    0.000003
-4998    0.000003
-4999    0.000003
-5000    0.000003
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-07-18
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.018475</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.000923</v>
-      </c>
-      <c r="F9" t="n">
-        <v>12154.195693</v>
-      </c>
-      <c r="G9" t="n">
-        <v>725.073792</v>
-      </c>
-      <c r="H9" t="n">
-        <v>83.403171</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-07-21
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-07-21
 0       0.000002
 1       0.000002
 2       0.000002
-3       0.000003
-4       0.000003
+3       0.000002
+4       0.000002
 ...          ...
 4996    0.000002
 4997    0.000002
@@ -1087,6 +1008,85 @@
 [5001 rows x 1 columns]</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-07-18
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.013243</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.000638</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10387.340775</v>
+      </c>
+      <c r="G9" t="n">
+        <v>664.209345</v>
+      </c>
+      <c r="H9" t="n">
+        <v>67.05647399999999</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-07-21
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-07-21
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
+...          ...
+4996    0.000002
+4997    0.000002
+4998    0.000002
+4999    0.000002
+5000    0.000002
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-07-21
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.013264</v>
+        <v>0.01189</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000813</v>
+        <v>0.00076</v>
       </c>
       <c r="F10" t="n">
-        <v>9087.076641</v>
+        <v>8506.847610000001</v>
       </c>
       <c r="G10" t="n">
-        <v>604.096764</v>
+        <v>579.698081</v>
       </c>
       <c r="H10" t="n">
-        <v>76.112899</v>
+        <v>76.149681</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.009115</v>
+        <v>0.008828000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000412</v>
+        <v>0.000358</v>
       </c>
       <c r="F11" t="n">
-        <v>6096.183655</v>
+        <v>5477.167708</v>
       </c>
       <c r="G11" t="n">
-        <v>353.924838</v>
+        <v>323.708447</v>
       </c>
       <c r="H11" t="n">
-        <v>41.916447</v>
+        <v>37.696753</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.012662</v>
+        <v>0.03887</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000734</v>
+        <v>0.002706</v>
       </c>
       <c r="F12" t="n">
-        <v>8773.480014999999</v>
+        <v>16660.052178</v>
       </c>
       <c r="G12" t="n">
-        <v>539.9313540000001</v>
+        <v>1117.904327</v>
       </c>
       <c r="H12" t="n">
-        <v>67.977825</v>
+        <v>159.4068</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1309,18 +1309,18 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2025-07-24
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
+          <t xml:space="preserve">        2025-07-24
+0     1.028098e-06
+1     1.030188e-06
+2     1.032252e-06
+3     1.034289e-06
+4     1.036299e-06
+...            ...
+4996  8.240318e-07
+4997  8.218089e-07
+4998  8.195812e-07
+4999  8.173486e-07
+5000  8.151114e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -1355,19 +1355,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.018785</v>
+        <v>0.011477</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001356</v>
+        <v>0.000795</v>
       </c>
       <c r="F13" t="n">
-        <v>12193.893401</v>
+        <v>9587.099765000001</v>
       </c>
       <c r="G13" t="n">
-        <v>789.482233</v>
+        <v>603.1805879999999</v>
       </c>
       <c r="H13" t="n">
-        <v>90.52716599999999</v>
+        <v>63.155255</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1388,7 +1388,86 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">        2025-07-25
+0     1.105518e-06
+1     1.107763e-06
+2     1.109979e-06
+3     1.112165e-06
+4     1.114324e-06
+...            ...
+4996  8.987630e-07
+4997  8.963358e-07
+4998  8.939033e-07
+4999  8.914657e-07
+5000  8.890229e-07
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">      2025-07-25
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.023484</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.001578</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13673.314875</v>
+      </c>
+      <c r="G14" t="n">
+        <v>880.041206</v>
+      </c>
+      <c r="H14" t="n">
+        <v>94.688318</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-07-28
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-07-28
 0       0.000001
 1       0.000001
 2       0.000001
@@ -1403,85 +1482,6 @@
 [5001 rows x 1 columns]</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-07-25
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.021759</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.001511</v>
-      </c>
-      <c r="F14" t="n">
-        <v>13203.137797</v>
-      </c>
-      <c r="G14" t="n">
-        <v>854.198819</v>
-      </c>
-      <c r="H14" t="n">
-        <v>91.41737999999999</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-07-28
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-07-28
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-07-28
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.027341</v>
+        <v>0.02251</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00199</v>
+        <v>0.001626</v>
       </c>
       <c r="F15" t="n">
-        <v>14560.226335</v>
+        <v>12960.571603</v>
       </c>
       <c r="G15" t="n">
-        <v>991.9162229999999</v>
+        <v>898.923378</v>
       </c>
       <c r="H15" t="n">
-        <v>143.32213</v>
+        <v>133.310039</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1547,17 +1547,17 @@
       <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-07-29
-0     1.144741e-06
-1     1.147086e-06
-2     1.149403e-06
-3     1.151691e-06
-4     1.153952e-06
+0     9.939432e-07
+1     9.959550e-07
+2     9.979408e-07
+3     9.999007e-07
+4     1.001835e-06
 ...            ...
-4996  9.530245e-07
-4997  9.504665e-07
-4998  9.479032e-07
-4999  9.453347e-07
-5000  9.427612e-07
+4996  8.309853e-07
+4997  8.287370e-07
+4998  8.264837e-07
+4999  8.242257e-07
+5000  8.219631e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -1592,19 +1592,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.172937</v>
+        <v>0.179359</v>
       </c>
       <c r="E16" t="n">
-        <v>0.009048</v>
+        <v>0.009467</v>
       </c>
       <c r="F16" t="n">
-        <v>34768.311006</v>
+        <v>35425.045822</v>
       </c>
       <c r="G16" t="n">
-        <v>1894.300282</v>
+        <v>1960.20999</v>
       </c>
       <c r="H16" t="n">
-        <v>212.21978</v>
+        <v>222.988217</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1626,17 +1626,17 @@
       <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-07-30
-0       0.000017
-1       0.000017
-2       0.000017
-3       0.000017
-4       0.000017
-...          ...
-4996    0.000014
-4997    0.000014
-4998    0.000014
-4999    0.000014
-5000    0.000014
+0       0.000015
+1       0.000015
+2       0.000015
+3       0.000015
+4       0.000015
+...          ...
+4996    0.000013
+4997    0.000013
+4998    0.000013
+4999    0.000013
+5000    0.000013
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -1671,19 +1671,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.007584</v>
+        <v>0.008971</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000218</v>
+        <v>0.000346</v>
       </c>
       <c r="F17" t="n">
-        <v>5202.613855</v>
+        <v>6735.11415</v>
       </c>
       <c r="G17" t="n">
-        <v>293.175514</v>
+        <v>388.596508</v>
       </c>
       <c r="H17" t="n">
-        <v>36.703381</v>
+        <v>48.854656</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1705,11 +1705,90 @@
       <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-07-31
-0       0.000007
-1       0.000007
-2       0.000007
-3       0.000007
-4       0.000007
+0       0.000005
+1       0.000005
+2       0.000005
+3       0.000005
+4       0.000005
+...          ...
+4996    0.000004
+4997    0.000004
+4998    0.000004
+4999    0.000004
+5000    0.000004
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-07-31
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.006477</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.000113</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3068.475928</v>
+      </c>
+      <c r="G18" t="n">
+        <v>183.487013</v>
+      </c>
+      <c r="H18" t="n">
+        <v>24.653519</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-08-04
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-08-04
+0       0.000006
+1       0.000006
+2       0.000006
+3       0.000006
+4       0.000006
 ...          ...
 4996    0.000005
 4997    0.000005
@@ -1719,85 +1798,6 @@
 [5001 rows x 1 columns]</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-07-31
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.005152</v>
-      </c>
-      <c r="E18" t="n">
-        <v>7.3e-05</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2176.74413</v>
-      </c>
-      <c r="G18" t="n">
-        <v>124.182533</v>
-      </c>
-      <c r="H18" t="n">
-        <v>16.586639</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-08-04
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-08-04
-0       0.000007
-1       0.000007
-2       0.000007
-3       0.000007
-4       0.000007
-...          ...
-4996    0.000006
-4997    0.000006
-4998    0.000006
-4999    0.000006
-5000    0.000006
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-08-04
@@ -1829,19 +1829,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.006042</v>
+        <v>0.00617</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000183</v>
+        <v>0.000179</v>
       </c>
       <c r="F19" t="n">
-        <v>5047.441507</v>
+        <v>4969.049205</v>
       </c>
       <c r="G19" t="n">
-        <v>281.937911</v>
+        <v>283.659144</v>
       </c>
       <c r="H19" t="n">
-        <v>27.549889</v>
+        <v>29.675563</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1908,19 +1908,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.006403</v>
+        <v>0.005811</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000132</v>
+        <v>0.000144</v>
       </c>
       <c r="F20" t="n">
-        <v>4830.942093</v>
+        <v>4942.542126</v>
       </c>
       <c r="G20" t="n">
-        <v>305.887921</v>
+        <v>320.913063</v>
       </c>
       <c r="H20" t="n">
-        <v>38.277893</v>
+        <v>39.588004</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-08-06
-0       0.000004
-1       0.000004
-2       0.000004
-3       0.000004
-4       0.000004
+0       0.000003
+1       0.000003
+2       0.000003
+3       0.000003
+4       0.000003
 ...          ...
 4996    0.000003
 4997    0.000003
@@ -1987,19 +1987,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.009808000000000001</v>
+        <v>0.009377999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000283</v>
+        <v>0.000239</v>
       </c>
       <c r="F21" t="n">
-        <v>6071.852169</v>
+        <v>5757.137602</v>
       </c>
       <c r="G21" t="n">
-        <v>366.757151</v>
+        <v>360.820345</v>
       </c>
       <c r="H21" t="n">
-        <v>44.277347</v>
+        <v>44.520155</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2021,11 +2021,11 @@
       <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-08-07
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
 ...          ...
 4996    0.000002
 4997    0.000002
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.011685</v>
+        <v>0.009523</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000426</v>
+        <v>0.000296</v>
       </c>
       <c r="F22" t="n">
-        <v>6660.86932</v>
+        <v>5563.605072</v>
       </c>
       <c r="G22" t="n">
-        <v>337.508879</v>
+        <v>297.171497</v>
       </c>
       <c r="H22" t="n">
-        <v>34.266131</v>
+        <v>35.97062</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2145,19 +2145,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.006036</v>
+        <v>0.005643</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000369</v>
+        <v>0.000334</v>
       </c>
       <c r="F23" t="n">
-        <v>7418.650992</v>
+        <v>7039.066057</v>
       </c>
       <c r="G23" t="n">
-        <v>476.390899</v>
+        <v>461.672528</v>
       </c>
       <c r="H23" t="n">
-        <v>51.234887</v>
+        <v>51.761311</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2179,11 +2179,11 @@
       <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-08-11
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
 ...          ...
 4996    0.000001
 4997    0.000001
@@ -2224,19 +2224,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.012438</v>
+        <v>0.011417</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000492</v>
+        <v>0.000496</v>
       </c>
       <c r="F24" t="n">
-        <v>7630.204635</v>
+        <v>7591.695598</v>
       </c>
       <c r="G24" t="n">
-        <v>436.626546</v>
+        <v>441.73451</v>
       </c>
       <c r="H24" t="n">
-        <v>48.467479</v>
+        <v>49.525356</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2258,17 +2258,17 @@
       <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-08-12
-0       0.000006
-1       0.000006
-2       0.000006
-3       0.000006
-4       0.000006
+0       0.000005
+1       0.000005
+2       0.000005
+3       0.000005
+4       0.000005
 ...          ...
 4996    0.000005
 4997    0.000005
 4998    0.000005
-4999    0.000005
-5000    0.000005
+4999    0.000004
+5000    0.000004
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -2303,19 +2303,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.023644</v>
+        <v>0.021993</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001491</v>
+        <v>0.001371</v>
       </c>
       <c r="F25" t="n">
-        <v>11991.24435</v>
+        <v>11447.759576</v>
       </c>
       <c r="G25" t="n">
-        <v>636.2758700000001</v>
+        <v>608.52667</v>
       </c>
       <c r="H25" t="n">
-        <v>48.52327</v>
+        <v>47.279388</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2382,19 +2382,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.011299</v>
+        <v>0.015374</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000579</v>
+        <v>0.000813</v>
       </c>
       <c r="F26" t="n">
-        <v>7623.723684</v>
+        <v>9388.921428</v>
       </c>
       <c r="G26" t="n">
-        <v>435.284974</v>
+        <v>541.607499</v>
       </c>
       <c r="H26" t="n">
-        <v>47.766159</v>
+        <v>61.209552</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2416,11 +2416,11 @@
       <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-08-14
-0       0.000004
-1       0.000004
-2       0.000004
-3       0.000004
-4       0.000004
+0       0.000003
+1       0.000003
+2       0.000003
+3       0.000003
+4       0.000003
 ...          ...
 4996    0.000003
 4997    0.000003
@@ -2461,19 +2461,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.008591</v>
+        <v>0.009513000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000367</v>
+        <v>0.000433</v>
       </c>
       <c r="F27" t="n">
-        <v>7187.903982</v>
+        <v>7706.481898</v>
       </c>
       <c r="G27" t="n">
-        <v>382.064241</v>
+        <v>408.113362</v>
       </c>
       <c r="H27" t="n">
-        <v>33.44811</v>
+        <v>37.835124</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2495,11 +2495,11 @@
       <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-08-15
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
 ...          ...
 4996    0.000001
 4997    0.000001
@@ -2540,19 +2540,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.048059</v>
+        <v>0.052607</v>
       </c>
       <c r="E28" t="n">
-        <v>0.003729</v>
+        <v>0.004091</v>
       </c>
       <c r="F28" t="n">
-        <v>21438.25261</v>
+        <v>22528.88224</v>
       </c>
       <c r="G28" t="n">
-        <v>1334.012173</v>
+        <v>1422.16404</v>
       </c>
       <c r="H28" t="n">
-        <v>161.120159</v>
+        <v>176.971861</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2573,18 +2573,18 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2025-08-18
-0       0.000001
-1       0.000001
-2       0.000001
-3       0.000001
-4       0.000001
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
+          <t xml:space="preserve">        2025-08-18
+0     1.070931e-06
+1     1.073097e-06
+2     1.075236e-06
+3     1.077347e-06
+4     1.079430e-06
+...            ...
+4996  9.006543e-07
+4997  8.982163e-07
+4998  8.957730e-07
+4999  8.933245e-07
+5000  8.908709e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -2619,19 +2619,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.045608</v>
+        <v>0.051875</v>
       </c>
       <c r="E29" t="n">
-        <v>0.002504</v>
+        <v>0.003045</v>
       </c>
       <c r="F29" t="n">
-        <v>18259.827806</v>
+        <v>20039.723452</v>
       </c>
       <c r="G29" t="n">
-        <v>1059.257747</v>
+        <v>1182.253893</v>
       </c>
       <c r="H29" t="n">
-        <v>122.992006</v>
+        <v>140.017583</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
       <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-08-19
-0       0.000009
-1       0.000009
-2       0.000009
-3       0.000009
-4       0.000009
+0       0.000008
+1       0.000008
+2       0.000008
+3       0.000008
+4       0.000008
 ...          ...
 4996    0.000006
 4997    0.000006
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.08507099999999999</v>
+        <v>0.07410799999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.006071</v>
+        <v>0.005289</v>
       </c>
       <c r="F30" t="n">
-        <v>26810.878224</v>
+        <v>24808.722346</v>
       </c>
       <c r="G30" t="n">
-        <v>1650.605177</v>
+        <v>1537.55696</v>
       </c>
       <c r="H30" t="n">
-        <v>207.303916</v>
+        <v>193.311008</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2777,19 +2777,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.018794</v>
+        <v>0.017118</v>
       </c>
       <c r="E31" t="n">
-        <v>0.000567</v>
+        <v>0.000614</v>
       </c>
       <c r="F31" t="n">
-        <v>9658.282365999999</v>
+        <v>9825.425174</v>
       </c>
       <c r="G31" t="n">
-        <v>573.6550559999999</v>
+        <v>609.269535</v>
       </c>
       <c r="H31" t="n">
-        <v>53.124334</v>
+        <v>61.617299</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2817,11 +2817,11 @@
 3       0.000003
 4       0.000003
 ...          ...
-4996    0.000003
-4997    0.000003
-4998    0.000003
-4999    0.000003
-5000    0.000003
+4996    0.000002
+4997    0.000002
+4998    0.000002
+4999    0.000002
+5000    0.000002
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -2856,19 +2856,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.014502</v>
+        <v>0.017027</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000677</v>
+        <v>0.000777</v>
       </c>
       <c r="F32" t="n">
-        <v>7716.052754</v>
+        <v>8526.620088</v>
       </c>
       <c r="G32" t="n">
-        <v>447.72847</v>
+        <v>528.18902</v>
       </c>
       <c r="H32" t="n">
-        <v>53.475847</v>
+        <v>65.389499</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2935,19 +2935,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.031944</v>
+        <v>0.08158600000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002084</v>
+        <v>0.005486</v>
       </c>
       <c r="F33" t="n">
-        <v>16828.99216</v>
+        <v>27242.36299</v>
       </c>
       <c r="G33" t="n">
-        <v>996.8296</v>
+        <v>1676.895901</v>
       </c>
       <c r="H33" t="n">
-        <v>118.676513</v>
+        <v>210.192478</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2968,18 +2968,18 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2025-08-25
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
+          <t xml:space="preserve">        2025-08-25
+0     7.639121e-07
+1     7.654614e-07
+2     7.669909e-07
+3     7.685004e-07
+4     7.699899e-07
+...            ...
+4996  6.242139e-07
+4997  6.225282e-07
+4998  6.208388e-07
+4999  6.191458e-07
+5000  6.174493e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3014,19 +3014,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.039839</v>
+        <v>0.027533</v>
       </c>
       <c r="E34" t="n">
-        <v>0.002896</v>
+        <v>0.002012</v>
       </c>
       <c r="F34" t="n">
-        <v>19589.247812</v>
+        <v>16369.767882</v>
       </c>
       <c r="G34" t="n">
-        <v>1224.95382</v>
+        <v>1051.710682</v>
       </c>
       <c r="H34" t="n">
-        <v>153.268041</v>
+        <v>134.96768</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
       <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-08-26
-0     1.138113e-06
-1     1.140455e-06
-2     1.142769e-06
-3     1.145055e-06
-4     1.147313e-06
+0     8.305940e-07
+1     8.322794e-07
+2     8.339433e-07
+3     8.355855e-07
+4     8.372060e-07
 ...            ...
-4996  9.093632e-07
-4997  9.069297e-07
-4998  9.044911e-07
-4999  9.020475e-07
-5000  8.995990e-07
+4996  6.765021e-07
+4997  6.746756e-07
+4998  6.728449e-07
+4999  6.710104e-07
+5000  6.691721e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3093,19 +3093,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.034313</v>
+        <v>0.033084</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002689</v>
+        <v>0.002598</v>
       </c>
       <c r="F35" t="n">
-        <v>18554.9877</v>
+        <v>18514.231778</v>
       </c>
       <c r="G35" t="n">
-        <v>1075.547693</v>
+        <v>1109.348659</v>
       </c>
       <c r="H35" t="n">
-        <v>106.639244</v>
+        <v>111.944015</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3172,19 +3172,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.017467</v>
+        <v>0.016201</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0006489999999999999</v>
+        <v>0.00072</v>
       </c>
       <c r="F36" t="n">
-        <v>9240.997142</v>
+        <v>9701.636592999999</v>
       </c>
       <c r="G36" t="n">
-        <v>597.676375</v>
+        <v>639.463887</v>
       </c>
       <c r="H36" t="n">
-        <v>59.71227</v>
+        <v>62.578542</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3212,11 +3212,11 @@
 3       0.000003
 4       0.000003
 ...          ...
-4996    0.000003
-4997    0.000003
-4998    0.000003
-4999    0.000003
-5000    0.000003
+4996    0.000002
+4997    0.000002
+4998    0.000002
+4999    0.000002
+5000    0.000002
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3251,19 +3251,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.072237</v>
+        <v>0.07451000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>0.005864</v>
+        <v>0.005874</v>
       </c>
       <c r="F37" t="n">
-        <v>27332.383533</v>
+        <v>27350.760511</v>
       </c>
       <c r="G37" t="n">
-        <v>1766.170735</v>
+        <v>1779.345432</v>
       </c>
       <c r="H37" t="n">
-        <v>229.341737</v>
+        <v>233.77975</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3285,17 +3285,17 @@
       <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-08-29
-0     1.116215e-06
-1     1.118504e-06
-2     1.120766e-06
-3     1.123000e-06
-4     1.125206e-06
+0     9.338170e-07
+1     9.357067e-07
+2     9.375721e-07
+3     9.394131e-07
+4     9.412297e-07
 ...            ...
-4996  9.187723e-07
-4997  9.163082e-07
-4998  9.138389e-07
-4999  9.113646e-07
-5000  9.088855e-07
+4996  7.811587e-07
+4997  7.790451e-07
+4998  7.769269e-07
+4999  7.748041e-07
+5000  7.726771e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3330,19 +3330,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.047109</v>
+        <v>0.040733</v>
       </c>
       <c r="E38" t="n">
-        <v>0.003681</v>
+        <v>0.003116</v>
       </c>
       <c r="F38" t="n">
-        <v>21018.442174</v>
+        <v>19536.637785</v>
       </c>
       <c r="G38" t="n">
-        <v>1404.386038</v>
+        <v>1302.902566</v>
       </c>
       <c r="H38" t="n">
-        <v>171.540905</v>
+        <v>159.218853</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3364,17 +3364,17 @@
       <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-09-01
-0     1.027700e-06
-1     1.029812e-06
-2     1.031899e-06
-3     1.033960e-06
-4     1.035996e-06
+0     9.421679e-07
+1     9.440794e-07
+2     9.459664e-07
+3     9.478289e-07
+4     9.496667e-07
 ...            ...
-4996  8.287126e-07
-4997  8.264934e-07
-4998  8.242696e-07
-4999  8.220412e-07
-5000  8.198085e-07
+4996  7.696280e-07
+4997  7.675491e-07
+4998  7.654656e-07
+4999  7.633776e-07
+5000  7.612853e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3409,19 +3409,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.040113</v>
+        <v>0.03747</v>
       </c>
       <c r="E39" t="n">
-        <v>0.001419</v>
+        <v>0.001331</v>
       </c>
       <c r="F39" t="n">
-        <v>13797.772605</v>
+        <v>13510.822569</v>
       </c>
       <c r="G39" t="n">
-        <v>789.6641990000001</v>
+        <v>789.14384</v>
       </c>
       <c r="H39" t="n">
-        <v>86.21838700000001</v>
+        <v>87.017476</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3443,17 +3443,17 @@
       <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-09-02
-0       0.000006
-1       0.000006
-2       0.000006
-3       0.000006
-4       0.000006
-...          ...
-4996    0.000005
-4997    0.000005
-4998    0.000005
-4999    0.000005
-5000    0.000005
+0       0.000005
+1       0.000005
+2       0.000005
+3       0.000005
+4       0.000005
+...          ...
+4996    0.000004
+4997    0.000004
+4998    0.000004
+4999    0.000004
+5000    0.000004
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3488,19 +3488,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.097593</v>
+        <v>0.08418200000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>0.007159</v>
+        <v>0.00628</v>
       </c>
       <c r="F40" t="n">
-        <v>31191.650374</v>
+        <v>29243.130914</v>
       </c>
       <c r="G40" t="n">
-        <v>2030.86808</v>
+        <v>1942.427574</v>
       </c>
       <c r="H40" t="n">
-        <v>272.267877</v>
+        <v>264.395122</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3522,17 +3522,17 @@
       <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-09-03
-0     1.003510e-06
-1     1.005573e-06
-2     1.007611e-06
-3     1.009624e-06
-4     1.011613e-06
+0     9.454855e-07
+1     9.474048e-07
+2     9.492995e-07
+3     9.511696e-07
+4     9.530149e-07
 ...            ...
-4996  8.057794e-07
-4997  8.036224e-07
-4998  8.014609e-07
-4999  7.992949e-07
-5000  7.971247e-07
+4996  7.679174e-07
+4997  7.658440e-07
+4998  7.637660e-07
+4999  7.616835e-07
+5000  7.595968e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3567,19 +3567,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.027594</v>
+        <v>0.025395</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00174</v>
+        <v>0.001593</v>
       </c>
       <c r="F41" t="n">
-        <v>13664.617193</v>
+        <v>12855.798577</v>
       </c>
       <c r="G41" t="n">
-        <v>854.8722760000001</v>
+        <v>837.335837</v>
       </c>
       <c r="H41" t="n">
-        <v>109.12182</v>
+        <v>108.0649</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3601,17 +3601,17 @@
       <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-09-04
-0     9.138555e-07
-1     9.157240e-07
-2     9.175700e-07
-3     9.193934e-07
-4     9.211943e-07
+0     8.420799e-07
+1     8.437807e-07
+2     8.454596e-07
+3     8.471165e-07
+4     8.487514e-07
 ...            ...
-4996  7.717751e-07
-4997  7.697021e-07
-4998  7.676247e-07
-4999  7.655432e-07
-5000  7.634576e-07
+4996  7.159709e-07
+4997  7.140319e-07
+4998  7.120886e-07
+4999  7.101412e-07
+5000  7.081899e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3646,19 +3646,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.044902</v>
+        <v>0.051247</v>
       </c>
       <c r="E42" t="n">
-        <v>0.002078</v>
+        <v>0.002391</v>
       </c>
       <c r="F42" t="n">
-        <v>16014.426697</v>
+        <v>17275.029433</v>
       </c>
       <c r="G42" t="n">
-        <v>894.066317</v>
+        <v>980.923715</v>
       </c>
       <c r="H42" t="n">
-        <v>102.202817</v>
+        <v>114.513471</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3680,17 +3680,17 @@
       <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-09-05
-0       0.000008
-1       0.000008
-2       0.000008
-3       0.000008
-4       0.000008
+0       0.000007
+1       0.000007
+2       0.000007
+3       0.000007
+4       0.000007
 ...          ...
 4996    0.000007
-4997    0.000007
-4998    0.000007
-4999    0.000007
-5000    0.000007
+4997    0.000006
+4998    0.000006
+4999    0.000006
+5000    0.000006
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3725,19 +3725,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.060542</v>
+        <v>0.06685199999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>0.004541</v>
+        <v>0.004925</v>
       </c>
       <c r="F43" t="n">
-        <v>22550.358834</v>
+        <v>23091.644342</v>
       </c>
       <c r="G43" t="n">
-        <v>1353.371989</v>
+        <v>1391.518474</v>
       </c>
       <c r="H43" t="n">
-        <v>162.367896</v>
+        <v>168.156212</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3758,18 +3758,18 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2025-09-08
-0       0.000001
-1       0.000001
-2       0.000001
-3       0.000001
-4       0.000001
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
+          <t xml:space="preserve">        2025-09-08
+0     1.192107e-06
+1     1.194532e-06
+2     1.196926e-06
+3     1.199289e-06
+4     1.201621e-06
+...            ...
+4996  9.549104e-07
+4997  9.523342e-07
+4998  9.497523e-07
+4999  9.471648e-07
+5000  9.445720e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3804,19 +3804,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.07656399999999999</v>
+        <v>0.09159100000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00538</v>
+        <v>0.006247</v>
       </c>
       <c r="F44" t="n">
-        <v>26958.517914</v>
+        <v>29036.341338</v>
       </c>
       <c r="G44" t="n">
-        <v>1730.214107</v>
+        <v>1908.32246</v>
       </c>
       <c r="H44" t="n">
-        <v>231.116056</v>
+        <v>266.904779</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3838,17 +3838,17 @@
       <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-09-09
-0     7.593200e-07
-1     7.608782e-07
-2     7.624176e-07
-3     7.639384e-07
-4     7.654404e-07
+0     5.043052e-07
+1     5.053279e-07
+2     5.063375e-07
+3     5.073339e-07
+4     5.083171e-07
 ...            ...
-4996  6.179715e-07
-4997  6.163161e-07
-4998  6.146572e-07
-4999  6.129949e-07
-5000  6.113293e-07
+4996  4.107062e-07
+4997  4.095977e-07
+4998  4.084867e-07
+4999  4.073734e-07
+5000  4.062577e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -3883,19 +3883,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.019845</v>
+        <v>0.029391</v>
       </c>
       <c r="E45" t="n">
-        <v>0.000723</v>
+        <v>0.00122</v>
       </c>
       <c r="F45" t="n">
-        <v>8019.438475</v>
+        <v>10202.801027</v>
       </c>
       <c r="G45" t="n">
-        <v>518.56917</v>
+        <v>695.859856</v>
       </c>
       <c r="H45" t="n">
-        <v>65.14607100000001</v>
+        <v>86.70520999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3962,19 +3962,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.019785</v>
+        <v>0.021179</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001488</v>
+        <v>0.001587</v>
       </c>
       <c r="F46" t="n">
-        <v>14230.202438</v>
+        <v>14763.561832</v>
       </c>
       <c r="G46" t="n">
-        <v>969.125312</v>
+        <v>1011.9044</v>
       </c>
       <c r="H46" t="n">
-        <v>106.699869</v>
+        <v>114.347148</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4002,11 +4002,11 @@
 3       0.000002
 4       0.000002
 ...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -4041,19 +4041,19 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.007796</v>
+        <v>0.00725</v>
       </c>
       <c r="E47" t="n">
-        <v>0.000366</v>
+        <v>0.00046</v>
       </c>
       <c r="F47" t="n">
-        <v>6481.826454</v>
+        <v>7273.808184</v>
       </c>
       <c r="G47" t="n">
-        <v>471.997875</v>
+        <v>542.780769</v>
       </c>
       <c r="H47" t="n">
-        <v>53.947913</v>
+        <v>66.97569</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4081,6 +4081,85 @@
 3       0.000002
 4       0.000002
 ...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-12
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.009580999999999999</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.000548</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8896.429587000001</v>
+      </c>
+      <c r="G48" t="n">
+        <v>601.103374</v>
+      </c>
+      <c r="H48" t="n">
+        <v>69.450193</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-15
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-15
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
+...          ...
 4996    0.000002
 4997    0.000002
 4998    0.000002
@@ -4089,85 +4168,6 @@
 [5001 rows x 1 columns]</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-12
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" t="n">
-        <v>46</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>0.007531</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.00028</v>
-      </c>
-      <c r="F48" t="n">
-        <v>6478.225254</v>
-      </c>
-      <c r="G48" t="n">
-        <v>431.338597</v>
-      </c>
-      <c r="H48" t="n">
-        <v>48.187614</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-15
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-15
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-09-15
@@ -4199,19 +4199,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.018695</v>
+        <v>0.025485</v>
       </c>
       <c r="E49" t="n">
-        <v>0.001344</v>
+        <v>0.002032</v>
       </c>
       <c r="F49" t="n">
-        <v>13960.308496</v>
+        <v>17121.563047</v>
       </c>
       <c r="G49" t="n">
-        <v>905.135034</v>
+        <v>1128.852936</v>
       </c>
       <c r="H49" t="n">
-        <v>103.920598</v>
+        <v>129.517273</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4233,17 +4233,17 @@
       <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-09-16
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
+...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.069081</v>
+        <v>0.086815</v>
       </c>
       <c r="E50" t="n">
-        <v>0.004328</v>
+        <v>0.005274</v>
       </c>
       <c r="F50" t="n">
-        <v>24711.647661</v>
+        <v>26955.325826</v>
       </c>
       <c r="G50" t="n">
-        <v>1463.689704</v>
+        <v>1619.721361</v>
       </c>
       <c r="H50" t="n">
-        <v>162.436045</v>
+        <v>182.054394</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4312,11 +4312,11 @@
       <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-09-17
-0       0.000005
-1       0.000005
-2       0.000005
-3       0.000005
-4       0.000005
+0       0.000004
+1       0.000004
+2       0.000004
+3       0.000004
+4       0.000004
 ...          ...
 4996    0.000004
 4997    0.000004
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.085893</v>
+        <v>0.086906</v>
       </c>
       <c r="E51" t="n">
-        <v>0.005946</v>
+        <v>0.00614</v>
       </c>
       <c r="F51" t="n">
-        <v>26549.605291</v>
+        <v>26329.584396</v>
       </c>
       <c r="G51" t="n">
-        <v>1557.90562</v>
+        <v>1558.147898</v>
       </c>
       <c r="H51" t="n">
-        <v>192.706152</v>
+        <v>194.254536</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -4391,17 +4391,17 @@
       <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-09-18
-0     1.050101e-06
-1     1.052256e-06
-2     1.054385e-06
-3     1.056489e-06
-4     1.058567e-06
+0     9.384930e-07
+1     9.403961e-07
+2     9.422748e-07
+3     9.441291e-07
+4     9.459588e-07
 ...            ...
-4996  8.573639e-07
-4997  8.550661e-07
-4998  8.527636e-07
-4999  8.504564e-07
-5000  8.481446e-07
+4996  7.703487e-07
+4997  7.682673e-07
+4998  7.661813e-07
+4999  7.640909e-07
+5000  7.619962e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -4436,19 +4436,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.018604</v>
+        <v>0.027248</v>
       </c>
       <c r="E52" t="n">
-        <v>0.001128</v>
+        <v>0.001927</v>
       </c>
       <c r="F52" t="n">
-        <v>12580.784166</v>
+        <v>16401.541512</v>
       </c>
       <c r="G52" t="n">
-        <v>783.732998</v>
+        <v>1028.49293</v>
       </c>
       <c r="H52" t="n">
-        <v>77.45003800000001</v>
+        <v>102.651654</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -4469,18 +4469,18 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2025-09-19
-0       0.000001
-1       0.000001
-2       0.000001
-3       0.000001
-4       0.000001
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
+          <t xml:space="preserve">        2025-09-19
+0     8.476109e-07
+1     8.493291e-07
+2     8.510252e-07
+3     8.526992e-07
+4     8.543511e-07
+...            ...
+4996  6.968147e-07
+4997  6.949319e-07
+4998  6.930450e-07
+4999  6.911541e-07
+5000  6.892592e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -4515,19 +4515,19 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.009934999999999999</v>
+        <v>0.012552</v>
       </c>
       <c r="E53" t="n">
-        <v>0.000444</v>
+        <v>0.000539</v>
       </c>
       <c r="F53" t="n">
-        <v>7491.646365</v>
+        <v>8455.677971999999</v>
       </c>
       <c r="G53" t="n">
-        <v>427.745803</v>
+        <v>491.169011</v>
       </c>
       <c r="H53" t="n">
-        <v>36.402021</v>
+        <v>41.404774</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4594,19 +4594,19 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.011855</v>
+        <v>0.013594</v>
       </c>
       <c r="E54" t="n">
-        <v>0.000431</v>
+        <v>0.000507</v>
       </c>
       <c r="F54" t="n">
-        <v>8445.930388000001</v>
+        <v>9091.093515</v>
       </c>
       <c r="G54" t="n">
-        <v>553.19271</v>
+        <v>585.706874</v>
       </c>
       <c r="H54" t="n">
-        <v>68.957939</v>
+        <v>74.876431</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4673,19 +4673,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.285987</v>
+        <v>0.269134</v>
       </c>
       <c r="E55" t="n">
-        <v>0.018887</v>
+        <v>0.017789</v>
       </c>
       <c r="F55" t="n">
-        <v>48302.182973</v>
+        <v>46650.028235</v>
       </c>
       <c r="G55" t="n">
-        <v>3204.940834</v>
+        <v>3088.700819</v>
       </c>
       <c r="H55" t="n">
-        <v>474.086115</v>
+        <v>453.599021</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4707,17 +4707,17 @@
       <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-09-24
-0     3.805004e-07
-1     3.812807e-07
-2     3.820517e-07
-3     3.828133e-07
-4     3.835655e-07
+0     3.617928e-07
+1     3.625256e-07
+2     3.632489e-07
+3     3.639629e-07
+4     3.646673e-07
 ...            ...
-4996  3.095888e-07
-4997  3.087599e-07
-4998  3.079293e-07
-4999  3.070970e-07
-5000  3.062630e-07
+4996  2.972735e-07
+4997  2.964708e-07
+4998  2.956663e-07
+4999  2.948601e-07
+5000  2.940522e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -4752,19 +4752,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.053293</v>
+        <v>0.053933</v>
       </c>
       <c r="E56" t="n">
-        <v>0.002996</v>
+        <v>0.002902</v>
       </c>
       <c r="F56" t="n">
-        <v>20001.767385</v>
+        <v>19832.521358</v>
       </c>
       <c r="G56" t="n">
-        <v>1232.758267</v>
+        <v>1237.178062</v>
       </c>
       <c r="H56" t="n">
-        <v>151.473198</v>
+        <v>154.762023</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4792,6 +4792,796 @@
 3       0.000002
 4       0.000002
 ...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-25
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.044256</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.003489</v>
+      </c>
+      <c r="F57" t="n">
+        <v>20605.043204</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1416.465653</v>
+      </c>
+      <c r="H57" t="n">
+        <v>208.000441</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-26
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2025-09-26
+0     1.127685e-06
+1     1.129974e-06
+2     1.132233e-06
+3     1.134463e-06
+4     1.136664e-06
+...            ...
+4996  9.210824e-07
+4997  9.185941e-07
+4998  9.161003e-07
+4999  9.136012e-07
+5000  9.110969e-07
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-26
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.020975</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.001275</v>
+      </c>
+      <c r="F58" t="n">
+        <v>12920.330185</v>
+      </c>
+      <c r="G58" t="n">
+        <v>797.186821</v>
+      </c>
+      <c r="H58" t="n">
+        <v>92.407799</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-29
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-29
+0       0.000004
+1       0.000004
+2       0.000004
+3       0.000004
+4       0.000004
+...          ...
+4996    0.000003
+4997    0.000003
+4998    0.000003
+4999    0.000003
+5000    0.000003
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-29
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.07174800000000001</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.004906</v>
+      </c>
+      <c r="F59" t="n">
+        <v>23577.658967</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1477.313674</v>
+      </c>
+      <c r="H59" t="n">
+        <v>178.674985</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-30
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2025-09-30
+0     1.235724e-06
+1     1.238234e-06
+2     1.240711e-06
+3     1.243157e-06
+4     1.245570e-06
+...            ...
+4996  1.002318e-06
+4997  9.996102e-07
+4998  9.968963e-07
+4999  9.941766e-07
+5000  9.914513e-07
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-09-30
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>58</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.008799</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.000375</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6532.457932</v>
+      </c>
+      <c r="G60" t="n">
+        <v>457.702294</v>
+      </c>
+      <c r="H60" t="n">
+        <v>71.186785</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-01
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-01
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
+...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-01
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>59</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.022898</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.001488</v>
+      </c>
+      <c r="F61" t="n">
+        <v>13943.716091</v>
+      </c>
+      <c r="G61" t="n">
+        <v>881.505028</v>
+      </c>
+      <c r="H61" t="n">
+        <v>101.203897</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-02
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-02
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
+...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-02
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>60</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.015711</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.001049</v>
+      </c>
+      <c r="F62" t="n">
+        <v>12862.644798</v>
+      </c>
+      <c r="G62" t="n">
+        <v>872.450061</v>
+      </c>
+      <c r="H62" t="n">
+        <v>105.325465</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-03
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2025-10-03
+0     1.136663e-06
+1     1.138966e-06
+2     1.141239e-06
+3     1.143482e-06
+4     1.145696e-06
+...            ...
+4996  9.427960e-07
+4997  9.402462e-07
+4998  9.376909e-07
+4999  9.351302e-07
+5000  9.325641e-07
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-03
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>61</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.012692</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.000895</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9742.940685</v>
+      </c>
+      <c r="G63" t="n">
+        <v>643.422688</v>
+      </c>
+      <c r="H63" t="n">
+        <v>86.679574</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-06
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2025-10-06
+0     1.225908e-06
+1     1.228398e-06
+2     1.230857e-06
+3     1.233283e-06
+4     1.235677e-06
+...            ...
+4996  9.946268e-07
+4997  9.919408e-07
+4998  9.892490e-07
+4999  9.865513e-07
+5000  9.838481e-07
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-06
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.024067</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.001514</v>
+      </c>
+      <c r="F64" t="n">
+        <v>12441.10825</v>
+      </c>
+      <c r="G64" t="n">
+        <v>764.6472680000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>75.848572</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-07
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-07
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
+...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-07
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>63</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.019909</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.00135</v>
+      </c>
+      <c r="F65" t="n">
+        <v>11217.148101</v>
+      </c>
+      <c r="G65" t="n">
+        <v>729.378613</v>
+      </c>
+      <c r="H65" t="n">
+        <v>90.364237</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-08
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2025-10-08
+0     1.188688e-06
+1     1.191097e-06
+2     1.193476e-06
+3     1.195823e-06
+4     1.198139e-06
+...            ...
+4996  9.855809e-07
+4997  9.829154e-07
+4998  9.802442e-07
+4999  9.775672e-07
+5000  9.748847e-07
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-08
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>64</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.012764</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.000514</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5800.04669</v>
+      </c>
+      <c r="G66" t="n">
+        <v>291.738986</v>
+      </c>
+      <c r="H66" t="n">
+        <v>32.555984</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-09
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-09
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
+...          ...
 4996    0.000002
 4997    0.000002
 4998    0.000002
@@ -4800,796 +5590,6 @@
 [5001 rows x 1 columns]</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-25
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" t="n">
-        <v>55</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0.037775</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.002999</v>
-      </c>
-      <c r="F57" t="n">
-        <v>19090.901376</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1285.884671</v>
-      </c>
-      <c r="H57" t="n">
-        <v>182.704421</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-26
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-26
-0       0.000001
-1       0.000001
-2       0.000001
-3       0.000001
-4       0.000001
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-26
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" t="n">
-        <v>56</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>0.022444</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.00129</v>
-      </c>
-      <c r="F58" t="n">
-        <v>13008.287597</v>
-      </c>
-      <c r="G58" t="n">
-        <v>784.22064</v>
-      </c>
-      <c r="H58" t="n">
-        <v>89.127498</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-29
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-29
-0       0.000005
-1       0.000005
-2       0.000005
-3       0.000005
-4       0.000005
-...          ...
-4996    0.000005
-4997    0.000005
-4998    0.000005
-4999    0.000005
-5000    0.000005
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-29
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" t="n">
-        <v>57</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0.06636300000000001</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.004589</v>
-      </c>
-      <c r="F59" t="n">
-        <v>22961.407107</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1411.096627</v>
-      </c>
-      <c r="H59" t="n">
-        <v>166.907481</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-30
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-30
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-09-30
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" t="n">
-        <v>58</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0.01195</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.000753</v>
-      </c>
-      <c r="F60" t="n">
-        <v>9292.592130000001</v>
-      </c>
-      <c r="G60" t="n">
-        <v>665.12152</v>
-      </c>
-      <c r="H60" t="n">
-        <v>99.550775</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-01
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-01
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-01
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" t="n">
-        <v>59</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>0.027329</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.001897</v>
-      </c>
-      <c r="F61" t="n">
-        <v>15937.199623</v>
-      </c>
-      <c r="G61" t="n">
-        <v>988.932418</v>
-      </c>
-      <c r="H61" t="n">
-        <v>107.74658</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-02
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-02
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-02
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" t="n">
-        <v>60</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>0.016369</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.001092</v>
-      </c>
-      <c r="F62" t="n">
-        <v>13033.600904</v>
-      </c>
-      <c r="G62" t="n">
-        <v>879.333031</v>
-      </c>
-      <c r="H62" t="n">
-        <v>103.734071</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-03
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        2025-10-03
-0     1.193754e-06
-1     1.196204e-06
-2     1.198623e-06
-3     1.201014e-06
-4     1.203374e-06
-...            ...
-4996  9.794131e-07
-4997  9.767870e-07
-4998  9.741553e-07
-4999  9.715184e-07
-5000  9.688762e-07
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-03
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" t="n">
-        <v>61</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>0.013788</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.000975</v>
-      </c>
-      <c r="F63" t="n">
-        <v>10321.514199</v>
-      </c>
-      <c r="G63" t="n">
-        <v>664.926073</v>
-      </c>
-      <c r="H63" t="n">
-        <v>87.61454999999999</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-06
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-06
-0       0.000001
-1       0.000001
-2       0.000001
-3       0.000001
-4       0.000001
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-06
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" t="n">
-        <v>62</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>0.019921</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.001094</v>
-      </c>
-      <c r="F64" t="n">
-        <v>10668.987371</v>
-      </c>
-      <c r="G64" t="n">
-        <v>610.318463</v>
-      </c>
-      <c r="H64" t="n">
-        <v>54.346854</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-07
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-07
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-07
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" t="n">
-        <v>63</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>0.016303</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.001067</v>
-      </c>
-      <c r="F65" t="n">
-        <v>9610.234563</v>
-      </c>
-      <c r="G65" t="n">
-        <v>629.593829</v>
-      </c>
-      <c r="H65" t="n">
-        <v>75.152046</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-08
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-08
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-08
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" t="n">
-        <v>64</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>0.018092</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.000753</v>
-      </c>
-      <c r="F66" t="n">
-        <v>8035.248981</v>
-      </c>
-      <c r="G66" t="n">
-        <v>398.732694</v>
-      </c>
-      <c r="H66" t="n">
-        <v>38.218806</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-09
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-09
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-10-09
@@ -5621,19 +5621,19 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.043362</v>
+        <v>0.032061</v>
       </c>
       <c r="E67" t="n">
-        <v>0.001999</v>
+        <v>0.001252</v>
       </c>
       <c r="F67" t="n">
-        <v>16682.542484</v>
+        <v>13278.537185</v>
       </c>
       <c r="G67" t="n">
-        <v>929.064378</v>
+        <v>736.621306</v>
       </c>
       <c r="H67" t="n">
-        <v>101.772192</v>
+        <v>81.448142</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5700,19 +5700,19 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.051626</v>
+        <v>0.063293</v>
       </c>
       <c r="E68" t="n">
-        <v>0.003697</v>
+        <v>0.004619</v>
       </c>
       <c r="F68" t="n">
-        <v>23449.77851</v>
+        <v>26374.740484</v>
       </c>
       <c r="G68" t="n">
-        <v>1471.974845</v>
+        <v>1684.920805</v>
       </c>
       <c r="H68" t="n">
-        <v>188.546202</v>
+        <v>218.428381</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5734,91 +5734,91 @@
       <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-10-13
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
+...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-13
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>67</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.026771</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.001597</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14384.55517</v>
+      </c>
+      <c r="G69" t="n">
+        <v>805.762197</v>
+      </c>
+      <c r="H69" t="n">
+        <v>72.39749999999999</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-14
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-14
 0       0.000002
 1       0.000002
 2       0.000002
 3       0.000002
 4       0.000002
 ...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-13
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" t="n">
-        <v>67</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0.025913</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.00142</v>
-      </c>
-      <c r="F69" t="n">
-        <v>13652.193973</v>
-      </c>
-      <c r="G69" t="n">
-        <v>756.211186</v>
-      </c>
-      <c r="H69" t="n">
-        <v>69.082908</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-14
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-14
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
-...          ...
 4996    0.000002
 4997    0.000002
 4998    0.000002
@@ -5858,19 +5858,19 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.013543</v>
+        <v>0.018791</v>
       </c>
       <c r="E70" t="n">
-        <v>0.000523</v>
+        <v>0.00077</v>
       </c>
       <c r="F70" t="n">
-        <v>8314.613828</v>
+        <v>10180.235152</v>
       </c>
       <c r="G70" t="n">
-        <v>471.166071</v>
+        <v>578.016243</v>
       </c>
       <c r="H70" t="n">
-        <v>57.594358</v>
+        <v>69.50682399999999</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.017093</v>
+        <v>0.015889</v>
       </c>
       <c r="E71" t="n">
-        <v>0.001038</v>
+        <v>0.001094</v>
       </c>
       <c r="F71" t="n">
-        <v>12850.459875</v>
+        <v>13155.74023</v>
       </c>
       <c r="G71" t="n">
-        <v>822.22579</v>
+        <v>868.061187</v>
       </c>
       <c r="H71" t="n">
-        <v>97.629034</v>
+        <v>102.564494</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5971,85 +5971,6 @@
       <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-10-16
-0       0.000004
-1       0.000004
-2       0.000004
-3       0.000004
-4       0.000004
-...          ...
-4996    0.000003
-4997    0.000003
-4998    0.000003
-4999    0.000003
-5000    0.000003
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-16
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" t="n">
-        <v>70</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0.009709000000000001</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.000416</v>
-      </c>
-      <c r="F72" t="n">
-        <v>7091.088868</v>
-      </c>
-      <c r="G72" t="n">
-        <v>397.868554</v>
-      </c>
-      <c r="H72" t="n">
-        <v>38.094715</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-17
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-17
 0       0.000003
 1       0.000003
 2       0.000003
@@ -6058,9 +5979,88 @@
 ...          ...
 4996    0.000003
 4997    0.000003
-4998    0.000003
-4999    0.000003
-5000    0.000003
+4998    0.000002
+4999    0.000002
+5000    0.000002
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-16
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>70</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.011141</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.000622</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8547.467639</v>
+      </c>
+      <c r="G72" t="n">
+        <v>489.483088</v>
+      </c>
+      <c r="H72" t="n">
+        <v>49.890764</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-17
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-17
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
+...          ...
+4996    0.000002
+4997    0.000002
+4998    0.000002
+4999    0.000002
+5000    0.000002
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -6095,19 +6095,19 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.012829</v>
+        <v>0.012846</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0007159999999999999</v>
+        <v>0.000867</v>
       </c>
       <c r="F73" t="n">
-        <v>9719.967789</v>
+        <v>10568.39792</v>
       </c>
       <c r="G73" t="n">
-        <v>591.247129</v>
+        <v>661.609009</v>
       </c>
       <c r="H73" t="n">
-        <v>68.875854</v>
+        <v>79.60525199999999</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -6135,11 +6135,11 @@
 3       0.000002
 4       0.000002
 ...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -6174,19 +6174,19 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.005863</v>
+        <v>0.005407</v>
       </c>
       <c r="E74" t="n">
-        <v>0.000292</v>
+        <v>0.000276</v>
       </c>
       <c r="F74" t="n">
-        <v>5026.810679</v>
+        <v>5154.377639</v>
       </c>
       <c r="G74" t="n">
-        <v>331.626868</v>
+        <v>340.799575</v>
       </c>
       <c r="H74" t="n">
-        <v>48.088995</v>
+        <v>51.189242</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6214,6 +6214,85 @@
 3       0.000002
 4       0.000002
 ...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-21
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.009318999999999999</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.000381</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5399.350537</v>
+      </c>
+      <c r="G75" t="n">
+        <v>272.104735</v>
+      </c>
+      <c r="H75" t="n">
+        <v>25.826895</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-22
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-22
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
+...          ...
 4996    0.000002
 4997    0.000002
 4998    0.000002
@@ -6222,85 +6301,6 @@
 [5001 rows x 1 columns]</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-21
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" t="n">
-        <v>73</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>0.011587</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.000418</v>
-      </c>
-      <c r="F75" t="n">
-        <v>6003.568073</v>
-      </c>
-      <c r="G75" t="n">
-        <v>296.084653</v>
-      </c>
-      <c r="H75" t="n">
-        <v>24.882341</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-22
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-22
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
-...          ...
-4996    0.000003
-4997    0.000003
-4998    0.000003
-4999    0.000003
-5000    0.000003
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-10-22
@@ -6332,19 +6332,19 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.021117</v>
+        <v>0.021672</v>
       </c>
       <c r="E76" t="n">
-        <v>0.001367</v>
+        <v>0.001485</v>
       </c>
       <c r="F76" t="n">
-        <v>13848.327198</v>
+        <v>14530.723024</v>
       </c>
       <c r="G76" t="n">
-        <v>878.421978</v>
+        <v>944.776325</v>
       </c>
       <c r="H76" t="n">
-        <v>115.512715</v>
+        <v>126.58739</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6366,11 +6366,11 @@
       <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-10-23
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
 ...          ...
 4996    0.000002
 4997    0.000002
@@ -6411,19 +6411,19 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.024242</v>
+        <v>0.036697</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00158</v>
+        <v>0.002677</v>
       </c>
       <c r="F77" t="n">
-        <v>14244.426513</v>
+        <v>18650.395647</v>
       </c>
       <c r="G77" t="n">
-        <v>967.399077</v>
+        <v>1288.925257</v>
       </c>
       <c r="H77" t="n">
-        <v>123.390269</v>
+        <v>171.995412</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6445,17 +6445,17 @@
       <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-10-24
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
+...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -6490,19 +6490,19 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.011359</v>
+        <v>0.016941</v>
       </c>
       <c r="E78" t="n">
-        <v>0.000352</v>
+        <v>0.000604</v>
       </c>
       <c r="F78" t="n">
-        <v>6753.735103</v>
+        <v>8888.651913</v>
       </c>
       <c r="G78" t="n">
-        <v>384.134652</v>
+        <v>526.911572</v>
       </c>
       <c r="H78" t="n">
-        <v>46.130214</v>
+        <v>66.110399</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6530,11 +6530,11 @@
 3       0.000005
 4       0.000005
 ...          ...
-4996    0.000005
-4997    0.000005
-4998    0.000005
-4999    0.000005
-5000    0.000005
+4996    0.000004
+4997    0.000004
+4998    0.000004
+4999    0.000004
+5000    0.000004
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -6569,19 +6569,19 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.050341</v>
+        <v>0.052522</v>
       </c>
       <c r="E79" t="n">
-        <v>0.002967</v>
+        <v>0.003116</v>
       </c>
       <c r="F79" t="n">
-        <v>21313.909975</v>
+        <v>21365.156477</v>
       </c>
       <c r="G79" t="n">
-        <v>1340.046469</v>
+        <v>1352.420058</v>
       </c>
       <c r="H79" t="n">
-        <v>172.702065</v>
+        <v>174.670555</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6603,17 +6603,17 @@
       <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-10-28
-0     8.918133e-07
-1     8.936410e-07
-2     8.954468e-07
-3     8.972305e-07
-4     8.989923e-07
+0     7.791582e-07
+1     7.807343e-07
+2     7.822901e-07
+3     7.838255e-07
+4     7.853406e-07
 ...            ...
-4996  7.364229e-07
-4997  7.344480e-07
-4998  7.324691e-07
-4999  7.304861e-07
-5000  7.284992e-07
+4996  6.527381e-07
+4997  6.509723e-07
+4998  6.492026e-07
+4999  6.474292e-07
+5000  6.456521e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -6648,19 +6648,19 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.008263</v>
+        <v>0.009233</v>
       </c>
       <c r="E80" t="n">
-        <v>0.000145</v>
+        <v>0.000279</v>
       </c>
       <c r="F80" t="n">
-        <v>2781.362625</v>
+        <v>4473.011301</v>
       </c>
       <c r="G80" t="n">
-        <v>146.666794</v>
+        <v>274.654291</v>
       </c>
       <c r="H80" t="n">
-        <v>15.41617</v>
+        <v>35.814078</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6682,164 +6682,6 @@
       <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-10-29
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-29
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" t="n">
-        <v>79</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>0.038498</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.002739</v>
-      </c>
-      <c r="F81" t="n">
-        <v>18369.388949</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1160.705383</v>
-      </c>
-      <c r="H81" t="n">
-        <v>144.023337</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-30
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-30
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-30
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" t="n">
-        <v>80</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>0.013186</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.000736</v>
-      </c>
-      <c r="F82" t="n">
-        <v>10173.357797</v>
-      </c>
-      <c r="G82" t="n">
-        <v>703.651166</v>
-      </c>
-      <c r="H82" t="n">
-        <v>98.754867</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-31
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-10-31
 0       0.000001
 1       0.000001
 2       0.000001
@@ -6854,6 +6696,164 @@
 [5001 rows x 1 columns]</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-29
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.093514</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.006745</v>
+      </c>
+      <c r="F81" t="n">
+        <v>29081.408019</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1891.777744</v>
+      </c>
+      <c r="H81" t="n">
+        <v>240.801474</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-30
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2025-10-30
+0     7.609243e-07
+1     7.624616e-07
+2     7.639790e-07
+3     7.654766e-07
+4     7.669542e-07
+...            ...
+4996  6.445989e-07
+4997  6.428535e-07
+4998  6.411042e-07
+4999  6.393513e-07
+5000  6.375948e-07
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-30
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.009070999999999999</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.000598</v>
+      </c>
+      <c r="F82" t="n">
+        <v>8976.42569</v>
+      </c>
+      <c r="G82" t="n">
+        <v>701.944024</v>
+      </c>
+      <c r="H82" t="n">
+        <v>101.772114</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-10-31
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2025-10-31
+0     8.119120e-07
+1     8.135569e-07
+2     8.151806e-07
+3     8.167832e-07
+4     8.183645e-07
+...            ...
+4996  6.706972e-07
+4997  6.688845e-07
+4998  6.670678e-07
+4999  6.652472e-07
+5000  6.634228e-07
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-10-31
@@ -6885,19 +6885,19 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.019749</v>
+        <v>0.018304</v>
       </c>
       <c r="E83" t="n">
-        <v>0.001298</v>
+        <v>0.00116</v>
       </c>
       <c r="F83" t="n">
-        <v>12139.394673</v>
+        <v>11240.694683</v>
       </c>
       <c r="G83" t="n">
-        <v>811.729081</v>
+        <v>773.312291</v>
       </c>
       <c r="H83" t="n">
-        <v>102.70702</v>
+        <v>99.852374</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6919,17 +6919,17 @@
       <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-11-03
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
+...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -6964,19 +6964,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.061946</v>
+        <v>0.048181</v>
       </c>
       <c r="E84" t="n">
-        <v>0.004189</v>
+        <v>0.003251</v>
       </c>
       <c r="F84" t="n">
-        <v>23398.437236</v>
+        <v>20195.63082</v>
       </c>
       <c r="G84" t="n">
-        <v>1577.819503</v>
+        <v>1397.390365</v>
       </c>
       <c r="H84" t="n">
-        <v>236.906568</v>
+        <v>215.25771</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6998,17 +6998,17 @@
       <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-11-04
-0     6.766379e-07
-1     6.780251e-07
-2     6.793957e-07
-3     6.807496e-07
-4     6.820867e-07
+0     6.440851e-07
+1     6.453892e-07
+2     6.466765e-07
+3     6.479469e-07
+4     6.492006e-07
 ...            ...
-4996  5.549240e-07
-4997  5.534369e-07
-4998  5.519466e-07
-4999  5.504534e-07
-5000  5.489572e-07
+4996  5.336976e-07
+4997  5.322551e-07
+4998  5.308094e-07
+4999  5.293607e-07
+5000  5.279090e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -7043,19 +7043,19 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.039814</v>
+        <v>0.035517</v>
       </c>
       <c r="E85" t="n">
-        <v>0.002746</v>
+        <v>0.002309</v>
       </c>
       <c r="F85" t="n">
-        <v>14815.986115</v>
+        <v>13669.925278</v>
       </c>
       <c r="G85" t="n">
-        <v>853.9828680000001</v>
+        <v>793.672891</v>
       </c>
       <c r="H85" t="n">
-        <v>77.01950100000001</v>
+        <v>74.980025</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -7122,19 +7122,19 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.009985000000000001</v>
+        <v>0.025377</v>
       </c>
       <c r="E86" t="n">
-        <v>0.000403</v>
+        <v>0.001297</v>
       </c>
       <c r="F86" t="n">
-        <v>8387.640519</v>
+        <v>13145.503152</v>
       </c>
       <c r="G86" t="n">
-        <v>582.24482</v>
+        <v>832.556995</v>
       </c>
       <c r="H86" t="n">
-        <v>66.218808</v>
+        <v>112.953199</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -7201,19 +7201,19 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.003748</v>
+        <v>0.004675</v>
       </c>
       <c r="E87" t="n">
-        <v>0.000149</v>
+        <v>0.000177</v>
       </c>
       <c r="F87" t="n">
-        <v>4459.651807</v>
+        <v>4993.597796</v>
       </c>
       <c r="G87" t="n">
-        <v>268.702779</v>
+        <v>298.950377</v>
       </c>
       <c r="H87" t="n">
-        <v>31.42426</v>
+        <v>37.083289</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -7235,12 +7235,486 @@
       <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-11-07
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
+...          ...
+4996    0.000001
+4997    0.000001
+4998    0.000001
+4999    0.000001
+5000    0.000001
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-07
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>86</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.007582</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.000376</v>
+      </c>
+      <c r="F88" t="n">
+        <v>6727.79473</v>
+      </c>
+      <c r="G88" t="n">
+        <v>412.856806</v>
+      </c>
+      <c r="H88" t="n">
+        <v>42.458759</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-10
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-10
 0       0.000002
 1       0.000002
 2       0.000002
 3       0.000002
 4       0.000002
 ...          ...
+4996    0.000002
+4997    0.000002
+4998    0.000002
+4999    0.000002
+5000    0.000002
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-10
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>87</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.020001</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.001057</v>
+      </c>
+      <c r="F89" t="n">
+        <v>9443.697077000001</v>
+      </c>
+      <c r="G89" t="n">
+        <v>527.414305</v>
+      </c>
+      <c r="H89" t="n">
+        <v>53.264608</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-11
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-11
+0       0.000003
+1       0.000004
+2       0.000004
+3       0.000004
+4       0.000004
+...          ...
+4996    0.000003
+4997    0.000003
+4998    0.000003
+4999    0.000003
+5000    0.000003
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-11
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>88</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.025365</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.001635</v>
+      </c>
+      <c r="F90" t="n">
+        <v>16261.838896</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1057.086022</v>
+      </c>
+      <c r="H90" t="n">
+        <v>123.300594</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-12
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2025-11-12
+0     1.193965e-06
+1     1.196389e-06
+2     1.198783e-06
+3     1.201145e-06
+4     1.203476e-06
+...            ...
+4996  9.713832e-07
+4997  9.687597e-07
+4998  9.661304e-07
+4999  9.634954e-07
+5000  9.608550e-07
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-12
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>89</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.03093</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.001728</v>
+      </c>
+      <c r="F91" t="n">
+        <v>15560.968991</v>
+      </c>
+      <c r="G91" t="n">
+        <v>936.5997609999999</v>
+      </c>
+      <c r="H91" t="n">
+        <v>108.111612</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-13
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-13
+0       0.000003
+1       0.000003
+2       0.000003
+3       0.000003
+4       0.000003
+...          ...
+4996    0.000002
+4997    0.000002
+4998    0.000002
+4999    0.000002
+5000    0.000002
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-13
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>90</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.02022</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="F92" t="n">
+        <v>13275.378551</v>
+      </c>
+      <c r="G92" t="n">
+        <v>776.932871</v>
+      </c>
+      <c r="H92" t="n">
+        <v>87.66411600000001</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-14
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-14
+0       0.000002
+1       0.000002
+2       0.000002
+3       0.000002
+4       0.000002
+...          ...
+4996    0.000002
+4997    0.000002
+4998    0.000002
+4999    0.000002
+5000    0.000002
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-14
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.020095</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.001281</v>
+      </c>
+      <c r="F93" t="n">
+        <v>13870.320355</v>
+      </c>
+      <c r="G93" t="n">
+        <v>898.630043</v>
+      </c>
+      <c r="H93" t="n">
+        <v>113.984309</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-17
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-17
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
+...          ...
 4996    0.000001
 4997    0.000001
 4998    0.000001
@@ -7249,229 +7723,71 @@
 [5001 rows x 1 columns]</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-07
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" t="n">
-        <v>86</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>0.007943</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0.000245</v>
-      </c>
-      <c r="F88" t="n">
-        <v>5828.625442</v>
-      </c>
-      <c r="G88" t="n">
-        <v>369.51867</v>
-      </c>
-      <c r="H88" t="n">
-        <v>39.065887</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-10
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-10
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-10
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" t="n">
-        <v>87</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0.00121</v>
-      </c>
-      <c r="F89" t="n">
-        <v>9814.585795999999</v>
-      </c>
-      <c r="G89" t="n">
-        <v>546.630007</v>
-      </c>
-      <c r="H89" t="n">
-        <v>55.206091</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-11
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-11
-0       0.000004
-1       0.000004
-2       0.000004
-3       0.000004
-4       0.000004
-...          ...
-4996    0.000003
-4997    0.000003
-4998    0.000003
-4999    0.000003
-5000    0.000003
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-11
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" t="n">
-        <v>88</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>0.020392</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0.001269</v>
-      </c>
-      <c r="F90" t="n">
-        <v>14028.803822</v>
-      </c>
-      <c r="G90" t="n">
-        <v>946.968215</v>
-      </c>
-      <c r="H90" t="n">
-        <v>109.732784</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-12
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-12
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-17
+0            0.0
+1            0.0
+2            0.0
+3            0.0
+4            0.0
+...          ...
+4996         0.0
+4997         0.0
+4998         0.0
+4999         0.0
+5000         0.0
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>92</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>KLE</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.022475</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.001445</v>
+      </c>
+      <c r="F94" t="n">
+        <v>14517.878761</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1022.11718</v>
+      </c>
+      <c r="H94" t="n">
+        <v>126.795058</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-18
+0      -0.018871
+1      -0.018863
+2      -0.018855
+3      -0.018847
+4      -0.018839
+...          ...
+4996    0.020117
+4997    0.020125
+4998    0.020132
+4999    0.020140
+5000    0.020148
+[5001 rows x 1 columns]</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2025-11-18
 0       0.000001
 1       0.000001
 2       0.000001
@@ -7486,322 +7802,6 @@
 [5001 rows x 1 columns]</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-12
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" t="n">
-        <v>89</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0.032709</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0.001787</v>
-      </c>
-      <c r="F91" t="n">
-        <v>15866.639015</v>
-      </c>
-      <c r="G91" t="n">
-        <v>939.483321</v>
-      </c>
-      <c r="H91" t="n">
-        <v>108.247845</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-13
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-13
-0       0.000004
-1       0.000004
-2       0.000004
-3       0.000004
-4       0.000004
-...          ...
-4996    0.000003
-4997    0.000003
-4998    0.000003
-4999    0.000003
-5000    0.000003
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-13
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" t="n">
-        <v>90</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>0.017999</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0.001279</v>
-      </c>
-      <c r="F92" t="n">
-        <v>12704.465371</v>
-      </c>
-      <c r="G92" t="n">
-        <v>741.450679</v>
-      </c>
-      <c r="H92" t="n">
-        <v>84.394339</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-14
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-14
-0       0.000003
-1       0.000003
-2       0.000003
-3       0.000003
-4       0.000003
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-14
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" t="n">
-        <v>91</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>0.018855</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0.001196</v>
-      </c>
-      <c r="F93" t="n">
-        <v>13415.272926</v>
-      </c>
-      <c r="G93" t="n">
-        <v>848.1721219999999</v>
-      </c>
-      <c r="H93" t="n">
-        <v>104.320665</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-17
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-17
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-17
-0            0.0
-1            0.0
-2            0.0
-3            0.0
-4            0.0
-...          ...
-4996         0.0
-4997         0.0
-4998         0.0
-4999         0.0
-5000         0.0
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" t="n">
-        <v>92</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>KLE</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>0.022312</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0.001314</v>
-      </c>
-      <c r="F94" t="n">
-        <v>14096.665123</v>
-      </c>
-      <c r="G94" t="n">
-        <v>926.040359</v>
-      </c>
-      <c r="H94" t="n">
-        <v>114.126906</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-18
-0      -0.018871
-1      -0.018863
-2      -0.018855
-3      -0.018847
-4      -0.018839
-...          ...
-4996    0.020117
-4997    0.020125
-4998    0.020132
-4999    0.020140
-5000    0.020148
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2025-11-18
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
-[5001 rows x 1 columns]</t>
-        </is>
-      </c>
       <c r="K94" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-11-18
@@ -7833,19 +7833,19 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.026474</v>
+        <v>0.05602</v>
       </c>
       <c r="E95" t="n">
-        <v>0.001798</v>
+        <v>0.003912</v>
       </c>
       <c r="F95" t="n">
-        <v>15128.234497</v>
+        <v>21479.419537</v>
       </c>
       <c r="G95" t="n">
-        <v>966.670621</v>
+        <v>1416.32943</v>
       </c>
       <c r="H95" t="n">
-        <v>121.902238</v>
+        <v>200.828117</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7866,18 +7866,18 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2025-11-19
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
+          <t xml:space="preserve">        2025-11-19
+0     6.918645e-07
+1     6.932682e-07
+2     6.946540e-07
+3     6.960218e-07
+4     6.973714e-07
+...            ...
+4996  5.621772e-07
+4997  5.606598e-07
+4998  5.591389e-07
+4999  5.576149e-07
+5000  5.560876e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -7912,19 +7912,19 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.029342</v>
+        <v>0.050406</v>
       </c>
       <c r="E96" t="n">
-        <v>0.001561</v>
+        <v>0.002574</v>
       </c>
       <c r="F96" t="n">
-        <v>12149.350205</v>
+        <v>16855.342396</v>
       </c>
       <c r="G96" t="n">
-        <v>715.005872</v>
+        <v>977.061023</v>
       </c>
       <c r="H96" t="n">
-        <v>84.10504899999999</v>
+        <v>115.776852</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7991,19 +7991,19 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.040076</v>
+        <v>0.056179</v>
       </c>
       <c r="E97" t="n">
-        <v>0.003068</v>
+        <v>0.004248</v>
       </c>
       <c r="F97" t="n">
-        <v>20249.796161</v>
+        <v>23684.766359</v>
       </c>
       <c r="G97" t="n">
-        <v>1267.579041</v>
+        <v>1456.209736</v>
       </c>
       <c r="H97" t="n">
-        <v>151.461889</v>
+        <v>171.54972</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -8024,18 +8024,18 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2025-11-24
-0       0.000001
-1       0.000001
-2       0.000001
-3       0.000001
-4       0.000001
-...          ...
-4996    0.000001
-4997    0.000001
-4998    0.000001
-4999    0.000001
-5000    0.000001
+          <t xml:space="preserve">        2025-11-24
+0     1.196178e-06
+1     1.198601e-06
+2     1.200992e-06
+3     1.203352e-06
+4     1.205681e-06
+...            ...
+4996  9.972973e-07
+4997  9.945987e-07
+4998  9.918942e-07
+4999  9.891840e-07
+5000  9.864682e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -8070,19 +8070,19 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.015142</v>
+        <v>0.015557</v>
       </c>
       <c r="E98" t="n">
-        <v>0.000699</v>
+        <v>0.000728</v>
       </c>
       <c r="F98" t="n">
-        <v>10488.838445</v>
+        <v>10686.974081</v>
       </c>
       <c r="G98" t="n">
-        <v>619.489331</v>
+        <v>639.348067</v>
       </c>
       <c r="H98" t="n">
-        <v>60.886183</v>
+        <v>62.349823</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -8149,19 +8149,19 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.027901</v>
+        <v>0.034325</v>
       </c>
       <c r="E99" t="n">
-        <v>0.002046</v>
+        <v>0.002676</v>
       </c>
       <c r="F99" t="n">
-        <v>17951.985769</v>
+        <v>19791.351457</v>
       </c>
       <c r="G99" t="n">
-        <v>1080.505408</v>
+        <v>1260.974838</v>
       </c>
       <c r="H99" t="n">
-        <v>110.247272</v>
+        <v>147.635028</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -8182,18 +8182,18 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2025-11-26
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
-...          ...
-4996    0.000002
-4997    0.000002
-4998    0.000002
-4999    0.000002
-5000    0.000002
+          <t xml:space="preserve">        2025-11-26
+0     1.145467e-06
+1     1.147777e-06
+2     1.150058e-06
+3     1.152309e-06
+4     1.154529e-06
+...            ...
+4996  9.913845e-07
+4997  9.886953e-07
+4998  9.860002e-07
+4999  9.832995e-07
+5000  9.805933e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -8228,19 +8228,19 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.297405</v>
+        <v>0.258869</v>
       </c>
       <c r="E100" t="n">
-        <v>0.020773</v>
+        <v>0.018346</v>
       </c>
       <c r="F100" t="n">
-        <v>53904.338329</v>
+        <v>50422.333749</v>
       </c>
       <c r="G100" t="n">
-        <v>3583.178663</v>
+        <v>3397.074241</v>
       </c>
       <c r="H100" t="n">
-        <v>478.901751</v>
+        <v>461.205602</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -8262,17 +8262,17 @@
       <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">        2025-11-27
-0     3.604966e-07
-1     3.612362e-07
-2     3.619670e-07
-3     3.626888e-07
-4     3.634018e-07
+0     3.407990e-07
+1     3.414895e-07
+2     3.421711e-07
+3     3.428439e-07
+4     3.435077e-07
 ...            ...
-4996  2.921984e-07
-4997  2.914163e-07
-4998  2.906325e-07
-4999  2.898472e-07
-5000  2.890603e-07
+4996  2.791378e-07
+4997  2.783842e-07
+4998  2.776290e-07
+4999  2.768722e-07
+5000  2.761137e-07
 [5001 rows x 1 columns]</t>
         </is>
       </c>
@@ -8307,19 +8307,19 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.021674</v>
+        <v>0.028129</v>
       </c>
       <c r="E101" t="n">
-        <v>0.001177</v>
+        <v>0.001563</v>
       </c>
       <c r="F101" t="n">
-        <v>9270.046531</v>
+        <v>11161.406212</v>
       </c>
       <c r="G101" t="n">
-        <v>612.468653</v>
+        <v>725.2052640000001</v>
       </c>
       <c r="H101" t="n">
-        <v>78.059308</v>
+        <v>87.592052</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -8341,11 +8341,11 @@
       <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">      2025-11-28
-0       0.000002
-1       0.000002
-2       0.000002
-3       0.000002
-4       0.000002
+0       0.000001
+1       0.000001
+2       0.000001
+3       0.000001
+4       0.000001
 ...          ...
 4996    0.000001
 4997    0.000001
